--- a/artfynd/A 36587-2025 artfynd.xlsx
+++ b/artfynd/A 36587-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1407,6 +1407,603 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134317502</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80486</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>627857</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7215408</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134317453</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>627467</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7215830</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134317447</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>627615</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7215651</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134317555</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80485</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>627857</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7215408</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134317546</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93256</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>627622</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7215635</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134317446</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>627549</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7215816</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36587-2025 artfynd.xlsx
+++ b/artfynd/A 36587-2025 artfynd.xlsx
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134317453</v>
+        <v>134317447</v>
       </c>
       <c r="B10" t="n">
         <v>57975</v>
@@ -1537,7 +1537,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627467</v>
+        <v>627615</v>
       </c>
       <c r="R10" t="n">
-        <v>7215830</v>
+        <v>7215651</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134317447</v>
+        <v>134317453</v>
       </c>
       <c r="B11" t="n">
         <v>57975</v>
@@ -1639,7 +1639,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>627615</v>
+        <v>627467</v>
       </c>
       <c r="R11" t="n">
-        <v>7215651</v>
+        <v>7215830</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 36587-2025 artfynd.xlsx
+++ b/artfynd/A 36587-2025 artfynd.xlsx
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134317447</v>
+        <v>134317453</v>
       </c>
       <c r="B10" t="n">
         <v>57975</v>
@@ -1537,7 +1537,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627615</v>
+        <v>627467</v>
       </c>
       <c r="R10" t="n">
-        <v>7215651</v>
+        <v>7215830</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134317453</v>
+        <v>134317447</v>
       </c>
       <c r="B11" t="n">
         <v>57975</v>
@@ -1639,7 +1639,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>627467</v>
+        <v>627615</v>
       </c>
       <c r="R11" t="n">
-        <v>7215830</v>
+        <v>7215651</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 36587-2025 artfynd.xlsx
+++ b/artfynd/A 36587-2025 artfynd.xlsx
@@ -1412,7 +1412,7 @@
         <v>134317502</v>
       </c>
       <c r="B9" t="n">
-        <v>80486</v>
+        <v>80493</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134317453</v>
+        <v>134317447</v>
       </c>
       <c r="B10" t="n">
         <v>57975</v>
@@ -1537,7 +1537,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627467</v>
+        <v>627615</v>
       </c>
       <c r="R10" t="n">
-        <v>7215830</v>
+        <v>7215651</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134317447</v>
+        <v>134317453</v>
       </c>
       <c r="B11" t="n">
         <v>57975</v>
@@ -1639,7 +1639,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>627615</v>
+        <v>627467</v>
       </c>
       <c r="R11" t="n">
-        <v>7215651</v>
+        <v>7215830</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1713,7 @@
         <v>134317555</v>
       </c>
       <c r="B12" t="n">
-        <v>80485</v>
+        <v>80492</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>134317546</v>
       </c>
       <c r="B13" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 36587-2025 artfynd.xlsx
+++ b/artfynd/A 36587-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121561180</v>
+        <v>121561160</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627750</v>
+        <v>627533</v>
       </c>
       <c r="R2" t="n">
-        <v>7215354</v>
+        <v>7215749</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121561161</v>
+        <v>121561163</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627533</v>
+        <v>627595</v>
       </c>
       <c r="R3" t="n">
-        <v>7215749</v>
+        <v>7215690</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121561167</v>
+        <v>134317546</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627613</v>
+        <v>627622</v>
       </c>
       <c r="R4" t="n">
-        <v>7215649</v>
+        <v>7215635</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -999,12 +969,7 @@
         <v>121561164</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,55 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121561176</v>
+        <v>134317555</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627737</v>
+        <v>627857</v>
       </c>
       <c r="R6" t="n">
-        <v>7215377</v>
+        <v>7215408</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,62 +1148,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121561160</v>
+        <v>134317502</v>
       </c>
       <c r="B7" t="n">
-        <v>92020</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80500</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627533</v>
+        <v>627857</v>
       </c>
       <c r="R7" t="n">
-        <v>7215749</v>
+        <v>7215408</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,62 +1245,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121561163</v>
+        <v>121561161</v>
       </c>
       <c r="B8" t="n">
-        <v>92004</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627595</v>
+        <v>627533</v>
       </c>
       <c r="R8" t="n">
-        <v>7215690</v>
+        <v>7215749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,45 +1359,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134317502</v>
+        <v>121561167</v>
       </c>
       <c r="B9" t="n">
-        <v>80493</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sågmyran, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627857</v>
+        <v>627613</v>
       </c>
       <c r="R9" t="n">
-        <v>7215408</v>
+        <v>7215649</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,12 +1429,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1449,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134317447</v>
+        <v>121561176</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,14 +1497,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sågmyran, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627615</v>
+        <v>627737</v>
       </c>
       <c r="R10" t="n">
-        <v>7215651</v>
+        <v>7215377</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,12 +1531,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,22 +1551,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134317453</v>
+        <v>121561180</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,19 +1594,19 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sågmyran, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>627467</v>
+        <v>627750</v>
       </c>
       <c r="R11" t="n">
-        <v>7215830</v>
+        <v>7215354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,12 +1633,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,57 +1653,62 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134317555</v>
+        <v>134317446</v>
       </c>
       <c r="B12" t="n">
-        <v>80492</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>627857</v>
+        <v>627549</v>
       </c>
       <c r="R12" t="n">
-        <v>7215408</v>
+        <v>7215816</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,45 +1767,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134317546</v>
+        <v>134317447</v>
       </c>
       <c r="B13" t="n">
-        <v>93264</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>627622</v>
+        <v>627615</v>
       </c>
       <c r="R13" t="n">
-        <v>7215635</v>
+        <v>7215651</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1869,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134317446</v>
+        <v>134317453</v>
       </c>
       <c r="B14" t="n">
         <v>57975</v>
@@ -1944,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>627549</v>
+        <v>627467</v>
       </c>
       <c r="R14" t="n">
-        <v>7215816</v>
+        <v>7215830</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,6 +1968,112 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134317439</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>627608</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7215679</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
